--- a/SGC-CKN/Excel/635b4c7a-47cd-4fb0-aa6e-3efb2b8d7062_Thi_công_cọc_khoan_nhồi_P7-18_D800_06-04-2026.xlsx
+++ b/SGC-CKN/Excel/635b4c7a-47cd-4fb0-aa6e-3efb2b8d7062_Thi_công_cọc_khoan_nhồi_P7-18_D800_06-04-2026.xlsx
@@ -53,7 +53,7 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>16:00 06/04/2026</t>
+    <t>16:10 06/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
@@ -157,7 +157,7 @@
     <t>Cát thô vừa, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">17:21
+    <t xml:space="preserve">18:21
 06/04/2026</t>
   </si>
   <si>
@@ -422,11 +422,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD9F99D"/>
       </patternFill>
     </fill>
@@ -438,6 +433,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -610,35 +610,35 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1253,7 +1253,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.565</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.94</v>
@@ -1262,10 +1262,10 @@
         <v>0.03</v>
       </c>
       <c r="I11" s="5">
-        <v>6.38</v>
+        <v>6.94</v>
       </c>
       <c r="J11" s="8">
-        <v>191.25</v>
+        <v>208.2</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1399,120 +1399,120 @@
         <v>-26.42</v>
       </c>
       <c r="H15" s="18">
-        <v>1.65</v>
+        <v>0.65</v>
       </c>
       <c r="I15" s="18">
         <v>4.98</v>
       </c>
-      <c r="J15" s="21">
-        <v>3.02</v>
+      <c r="J15" s="8">
+        <v>7.66</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="21">
         <v>-26.42</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="21">
         <v>-36.11</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="21">
         <v>1.5</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="21">
         <v>9.69</v>
       </c>
       <c r="J16" s="8">
         <v>6.46</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <v>-36.11</v>
       </c>
-      <c r="G17" s="25">
-        <v>-39.25</v>
-      </c>
-      <c r="H17" s="25">
+      <c r="G17" s="24">
+        <v>-38.25</v>
+      </c>
+      <c r="H17" s="24">
         <v>0.37</v>
       </c>
-      <c r="I17" s="25">
-        <v>3.14</v>
+      <c r="I17" s="24">
+        <v>2.14</v>
       </c>
       <c r="J17" s="8">
-        <v>8.56</v>
-      </c>
-      <c r="K17" s="26" t="s">
+        <v>5.84</v>
+      </c>
+      <c r="K17" s="25" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="F18" s="28">
-        <v>-39.25</v>
-      </c>
-      <c r="G18" s="28">
+      <c r="F18" s="27">
+        <v>-38.25</v>
+      </c>
+      <c r="G18" s="27">
         <v>-40</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="27">
         <v>0.52</v>
       </c>
-      <c r="I18" s="28">
-        <v>0.75</v>
-      </c>
-      <c r="J18" s="21">
-        <v>1.45</v>
-      </c>
-      <c r="K18" s="29" t="s">
+      <c r="I18" s="27">
+        <v>1.75</v>
+      </c>
+      <c r="J18" s="30">
+        <v>3.39</v>
+      </c>
+      <c r="K18" s="28" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.56</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.94</v>
@@ -1744,10 +1744,10 @@
         <v>0.03</v>
       </c>
       <c r="H2" s="5">
-        <v>6.38</v>
+        <v>6.94</v>
       </c>
       <c r="I2" s="8">
-        <v>191.25</v>
+        <v>208.2</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1857,38 +1857,38 @@
         <v>-26.42</v>
       </c>
       <c r="G6" s="18">
-        <v>1.65</v>
+        <v>0.65</v>
       </c>
       <c r="H6" s="18">
         <v>4.98</v>
       </c>
-      <c r="I6" s="21">
-        <v>3.02</v>
+      <c r="I6" s="8">
+        <v>7.66</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="21">
         <v>-26.42</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="21">
         <v>-36.11</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="21">
         <v>1.5</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <v>9.69</v>
       </c>
       <c r="I7" s="8">
@@ -1896,61 +1896,61 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="24">
         <v>-36.11</v>
       </c>
-      <c r="F8" s="25">
-        <v>-39.25</v>
-      </c>
-      <c r="G8" s="25">
+      <c r="F8" s="24">
+        <v>-38.25</v>
+      </c>
+      <c r="G8" s="24">
         <v>0.37</v>
       </c>
-      <c r="H8" s="25">
-        <v>3.14</v>
+      <c r="H8" s="24">
+        <v>2.14</v>
       </c>
       <c r="I8" s="8">
-        <v>8.56</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
+      <c r="A9" s="27">
         <v>8</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="27">
         <v>1</v>
       </c>
-      <c r="E9" s="28">
-        <v>-39.25</v>
-      </c>
-      <c r="F9" s="28">
+      <c r="E9" s="27">
+        <v>-38.25</v>
+      </c>
+      <c r="F9" s="27">
         <v>-40</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="27">
         <v>0.52</v>
       </c>
-      <c r="H9" s="28">
-        <v>0.75</v>
-      </c>
-      <c r="I9" s="21">
-        <v>1.45</v>
+      <c r="H9" s="27">
+        <v>1.75</v>
+      </c>
+      <c r="I9" s="30">
+        <v>3.39</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2025,19 +2025,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>-0.56</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
         <v>-45</v>
       </c>
       <c r="G12" s="40">
-        <v>7.63</v>
+        <v>6.63</v>
       </c>
       <c r="H12" s="40">
-        <v>44.44</v>
+        <v>45</v>
       </c>
       <c r="I12" s="40">
-        <v>5.82</v>
+        <v>6.78</v>
       </c>
     </row>
   </sheetData>
